--- a/website/examples/example_odk_nfc_tag_wipe.xlsx
+++ b/website/examples/example_odk_nfc_tag_wipe.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R3c95aa2c63904c34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R8ad00c3e30fc4f47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R26455c33d73e4488"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R018ecad45b63441a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R8d4afa0764764d9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R18a1d557fad94fb0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -360,7 +360,7 @@
         <x:v>field-list</x:v>
       </x:c>
       <x:c r="F5" s="3" t="str">
-        <x:v>com.example.researchos.EXECUTE_METHOD(method_id='nfc_tag_wipe',return_mode='flat')</x:v>
+        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='nfc_tag_wipe',return_mode='flat')</x:v>
       </x:c>
       <x:c r="G5" s="3" t="str"/>
     </x:row>
@@ -369,10 +369,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B6" s="3" t="str">
-        <x:v>researchos_execution_id</x:v>
+        <x:v>methodmesh_execution_id</x:v>
       </x:c>
       <x:c r="C6" s="3" t="str">
-        <x:v>ResearchOS execution ID</x:v>
+        <x:v>MethodMesh execution ID</x:v>
       </x:c>
       <x:c r="D6" s="3" t="str"/>
       <x:c r="E6" s="3" t="str"/>
@@ -386,10 +386,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B7" s="3" t="str">
-        <x:v>researchos_status</x:v>
+        <x:v>methodmesh_status</x:v>
       </x:c>
       <x:c r="C7" s="3" t="str">
-        <x:v>ResearchOS status</x:v>
+        <x:v>MethodMesh status</x:v>
       </x:c>
       <x:c r="D7" s="3" t="str"/>
       <x:c r="E7" s="3" t="str"/>
